--- a/Gravedigger2026/Assets/ConfigTables/Mode2/Excel/挖坟_坟墓品质定义表_Dig_GraveQualityConfig.xlsx
+++ b/Gravedigger2026/Assets/ConfigTables/Mode2/Excel/挖坟_坟墓品质定义表_Dig_GraveQualityConfig.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="93">
   <si>
     <t>坟墓品质ID</t>
   </si>
@@ -40,6 +40,9 @@
     <t>总血量</t>
   </si>
   <si>
+    <t>掉落模式</t>
+  </si>
+  <si>
     <t>掉落内容</t>
   </si>
   <si>
@@ -58,7 +61,10 @@
     <t>生成时初始化坟的 maxHP / 当前 HP</t>
   </si>
   <si>
-    <t>挖掘成功（HP=0）时产出；编码 Id_Count|…</t>
+    <t>1=每段独立万分比；2=权重抽恰好 1 项；后续可扩展</t>
+  </si>
+  <si>
+    <t>挖掘成功（HP=0）时产出；编码 Id;Weight;Count|…；权重用法见 DropMode</t>
   </si>
   <si>
     <t>剩余 HP%&gt;65%；空=品质默认</t>
@@ -76,6 +82,9 @@
     <t>MaxHP</t>
   </si>
   <si>
+    <t>DropMode</t>
+  </si>
+  <si>
     <t>LootDrop</t>
   </si>
   <si>
@@ -94,7 +103,10 @@
     <t>26</t>
   </si>
   <si>
-    <t>BP_Head_Human_1</t>
+    <t>1</t>
+  </si>
+  <si>
+    <t>BP_Head_Undead_1;10000;2|BP_Arm_Undead_2;10000;2</t>
   </si>
   <si>
     <t>GraveIcon_Q1_High</t>
@@ -109,7 +121,7 @@
     <t>Q2</t>
   </si>
   <si>
-    <t>BP_Torso_Human_1</t>
+    <t>BP_Torso_Undead_1;10000;2|BP_Leg_Undead_2;10000;2</t>
   </si>
   <si>
     <t>GraveIcon_Q2_High</t>
@@ -124,7 +136,7 @@
     <t>Q3</t>
   </si>
   <si>
-    <t>BP_Arm_Human_1</t>
+    <t>BP_Arm_Undead_Warrior;10000;1|BP_Head_Demon;10000;2</t>
   </si>
   <si>
     <t>GraveIcon_Q3_High</t>
@@ -139,7 +151,7 @@
     <t>Q4</t>
   </si>
   <si>
-    <t>BP_Arm_Elf_1</t>
+    <t>BP_Arm_Undead_Archer;10000;1|BP_Torso_Demon;10000;2</t>
   </si>
   <si>
     <t>GraveIcon_Q4_High</t>
@@ -154,7 +166,7 @@
     <t>Q5</t>
   </si>
   <si>
-    <t>BP_Arm_Orc_1</t>
+    <t>BP_Arm_Undead_Mage;10000;1|BP_Arm_Demon;10000;2</t>
   </si>
   <si>
     <t>GraveIcon_Q5_High</t>
@@ -169,7 +181,7 @@
     <t>Q6</t>
   </si>
   <si>
-    <t>BP_Arm_Undead_1</t>
+    <t>BP_Arm_Undead_Rogue;10000;1|BP_Leg_Demon;10000;2</t>
   </si>
   <si>
     <t>GraveIcon_Q6_High</t>
@@ -184,7 +196,7 @@
     <t>Q7</t>
   </si>
   <si>
-    <t>BP_Arm_Dwarf_1</t>
+    <t>BP_Arm_Undead_Guardian;10000;1</t>
   </si>
   <si>
     <t>GraveIcon_Q7_High</t>
@@ -199,7 +211,7 @@
     <t>Q8</t>
   </si>
   <si>
-    <t>BP_Arm_Goblin_1</t>
+    <t>BP_Arm_Undead_BombMaster;10000;1</t>
   </si>
   <si>
     <t>GraveIcon_Q8_High</t>
@@ -214,7 +226,7 @@
     <t>Q9</t>
   </si>
   <si>
-    <t>BP_Arm_Demon_1</t>
+    <t>BP_Arm_Undead_IceMage;10000;1</t>
   </si>
   <si>
     <t>GraveIcon_Q9_High</t>
@@ -229,7 +241,7 @@
     <t>Q10</t>
   </si>
   <si>
-    <t>BP_Arm_Angel_1</t>
+    <t>BP_Arm_Undead_Brawler;10000;1</t>
   </si>
   <si>
     <t>GraveIcon_Q10_High</t>
@@ -244,55 +256,61 @@
     <t>Q11</t>
   </si>
   <si>
-    <t>BP_Arm_Beast_1</t>
+    <t>BP_Arm_Undead_Berserker;10000;1</t>
   </si>
   <si>
     <t>Q12</t>
   </si>
   <si>
-    <t>BP_Arm_Construct_1</t>
+    <t>BP_Arm_Undead_Longbowman;10000;1</t>
   </si>
   <si>
     <t>Q13</t>
   </si>
   <si>
+    <t>BP_Arm_Undead_FireMage;10000;1</t>
+  </si>
+  <si>
     <t>Q14</t>
   </si>
   <si>
+    <t>BP_Arm_Undead_Shadowblade;10000;1</t>
+  </si>
+  <si>
     <t>Q15</t>
   </si>
   <si>
-    <t>BP_Leg_Elf_1</t>
+    <t>BP_Arm_Angel_Paladin;10000;1</t>
   </si>
   <si>
     <t>Q16</t>
   </si>
   <si>
-    <t>BP_Head_Orc_1</t>
+    <t>BP_Arm_Demon_DarkMage;10000;1</t>
   </si>
   <si>
     <t>Q17</t>
   </si>
   <si>
-    <t>BP_Torso_Orc_1</t>
+    <t>BP_Arm_Undead_1;10000;2|BP_Head_Angel;10000;2</t>
   </si>
   <si>
     <t>Q18</t>
   </si>
   <si>
-    <t>BP_Leg_Dwarf_1</t>
+    <t>BP_Leg_Undead_1;10000;2|BP_Torso_Angel;10000;2</t>
   </si>
   <si>
     <t>Q19</t>
   </si>
   <si>
-    <t>BP_Head_Demon_1</t>
+    <t>BP_Head_Undead_2;10000;2|BP_Arm_Angel;10000;2</t>
   </si>
   <si>
     <t>Q20</t>
   </si>
   <si>
-    <t>BP_Torso_Angel_1</t>
+    <t>BP_Torso_Undead_2;10000;2|BP_Leg_Angel;10000;2</t>
   </si>
 </sst>
 </file>
@@ -767,155 +785,154 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="33" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1262,13 +1279,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F23"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
+  <dimension ref="A1:G23"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
   <cols>
-    <col min="3" max="3" width="21.75" customWidth="1"/>
+    <col min="4" max="4" width="35.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:7">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1287,445 +1304,514 @@
       <c r="F1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:6">
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="3" s="1" customFormat="1" spans="1:6">
+        <v>12</v>
+      </c>
+      <c r="G2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" spans="1:7">
       <c r="A3" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
+        <v>19</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B4" t="s">
-        <v>19</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
+      </c>
+      <c r="C4" t="s">
+        <v>23</v>
       </c>
       <c r="D4" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E4" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F4" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
+        <v>26</v>
+      </c>
+      <c r="G4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="B5" t="s">
-        <v>19</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>25</v>
+        <v>22</v>
+      </c>
+      <c r="C5" t="s">
+        <v>23</v>
       </c>
       <c r="D5" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E5" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F5" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
+        <v>31</v>
+      </c>
+      <c r="G5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="B6" t="s">
-        <v>19</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>30</v>
+        <v>22</v>
+      </c>
+      <c r="C6" t="s">
+        <v>23</v>
       </c>
       <c r="D6" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="E6" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F6" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
+        <v>36</v>
+      </c>
+      <c r="G6" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
       <c r="A7" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="B7" t="s">
-        <v>19</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>35</v>
+        <v>22</v>
+      </c>
+      <c r="C7" t="s">
+        <v>23</v>
       </c>
       <c r="D7" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="E7" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F7" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
+        <v>41</v>
+      </c>
+      <c r="G7" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
       <c r="A8" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B8" t="s">
-        <v>19</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>40</v>
+        <v>22</v>
+      </c>
+      <c r="C8" t="s">
+        <v>23</v>
       </c>
       <c r="D8" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="E8" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F8" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
+        <v>46</v>
+      </c>
+      <c r="G8" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
       <c r="A9" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="B9" t="s">
-        <v>19</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>45</v>
+        <v>22</v>
+      </c>
+      <c r="C9" t="s">
+        <v>23</v>
       </c>
       <c r="D9" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="E9" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="F9" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
+        <v>51</v>
+      </c>
+      <c r="G9" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
       <c r="A10" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="B10" t="s">
-        <v>19</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>50</v>
+        <v>22</v>
+      </c>
+      <c r="C10" t="s">
+        <v>23</v>
       </c>
       <c r="D10" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="E10" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="F10" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
+        <v>56</v>
+      </c>
+      <c r="G10" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
       <c r="A11" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="B11" t="s">
-        <v>19</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>55</v>
+        <v>22</v>
+      </c>
+      <c r="C11" t="s">
+        <v>23</v>
       </c>
       <c r="D11" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="E11" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="F11" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
+        <v>61</v>
+      </c>
+      <c r="G11" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
       <c r="A12" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="B12" t="s">
-        <v>19</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>60</v>
+        <v>22</v>
+      </c>
+      <c r="C12" t="s">
+        <v>23</v>
       </c>
       <c r="D12" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="E12" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="F12" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
+        <v>66</v>
+      </c>
+      <c r="G12" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
       <c r="A13" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="B13" t="s">
-        <v>19</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>65</v>
+        <v>22</v>
+      </c>
+      <c r="C13" t="s">
+        <v>23</v>
       </c>
       <c r="D13" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="E13" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="F13" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
+        <v>71</v>
+      </c>
+      <c r="G13" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
       <c r="A14" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="B14" t="s">
-        <v>19</v>
-      </c>
-      <c r="C14" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C14" t="s">
+        <v>23</v>
+      </c>
+      <c r="D14" t="s">
+        <v>74</v>
+      </c>
+      <c r="E14" t="s">
         <v>70</v>
       </c>
-      <c r="D14" t="s">
-        <v>66</v>
-      </c>
-      <c r="E14" t="s">
-        <v>67</v>
-      </c>
       <c r="F14" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
+        <v>71</v>
+      </c>
+      <c r="G14" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
       <c r="A15" t="s">
+        <v>75</v>
+      </c>
+      <c r="B15" t="s">
+        <v>22</v>
+      </c>
+      <c r="C15" t="s">
+        <v>23</v>
+      </c>
+      <c r="D15" t="s">
+        <v>76</v>
+      </c>
+      <c r="E15" t="s">
+        <v>70</v>
+      </c>
+      <c r="F15" t="s">
         <v>71</v>
       </c>
-      <c r="B15" t="s">
-        <v>19</v>
-      </c>
-      <c r="C15" s="2" t="s">
+      <c r="G15" t="s">
         <v>72</v>
       </c>
-      <c r="D15" t="s">
-        <v>66</v>
-      </c>
-      <c r="E15" t="s">
-        <v>67</v>
-      </c>
-      <c r="F15" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
+    </row>
+    <row r="16" spans="1:7">
       <c r="A16" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="B16" t="s">
-        <v>19</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>30</v>
+        <v>22</v>
+      </c>
+      <c r="C16" t="s">
+        <v>23</v>
       </c>
       <c r="D16" t="s">
-        <v>66</v>
+        <v>78</v>
       </c>
       <c r="E16" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="F16" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
+        <v>71</v>
+      </c>
+      <c r="G16" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
       <c r="A17" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="B17" t="s">
-        <v>19</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>40</v>
+        <v>22</v>
+      </c>
+      <c r="C17" t="s">
+        <v>23</v>
       </c>
       <c r="D17" t="s">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="E17" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="F17" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
+        <v>71</v>
+      </c>
+      <c r="G17" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
       <c r="A18" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="B18" t="s">
-        <v>19</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>76</v>
+        <v>22</v>
+      </c>
+      <c r="C18" t="s">
+        <v>23</v>
       </c>
       <c r="D18" t="s">
-        <v>66</v>
+        <v>82</v>
       </c>
       <c r="E18" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="F18" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
+        <v>71</v>
+      </c>
+      <c r="G18" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
       <c r="A19" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="B19" t="s">
-        <v>19</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>78</v>
+        <v>22</v>
+      </c>
+      <c r="C19" t="s">
+        <v>23</v>
       </c>
       <c r="D19" t="s">
-        <v>66</v>
+        <v>84</v>
       </c>
       <c r="E19" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="F19" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
+        <v>71</v>
+      </c>
+      <c r="G19" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
       <c r="A20" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="B20" t="s">
-        <v>19</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>80</v>
+        <v>22</v>
+      </c>
+      <c r="C20" t="s">
+        <v>23</v>
       </c>
       <c r="D20" t="s">
-        <v>66</v>
+        <v>86</v>
       </c>
       <c r="E20" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="F20" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
+        <v>71</v>
+      </c>
+      <c r="G20" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
       <c r="A21" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="B21" t="s">
-        <v>19</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>82</v>
+        <v>22</v>
+      </c>
+      <c r="C21" t="s">
+        <v>23</v>
       </c>
       <c r="D21" t="s">
-        <v>66</v>
+        <v>88</v>
       </c>
       <c r="E21" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="F21" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
+        <v>71</v>
+      </c>
+      <c r="G21" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
       <c r="A22" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="B22" t="s">
-        <v>19</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>84</v>
+        <v>22</v>
+      </c>
+      <c r="C22" t="s">
+        <v>23</v>
       </c>
       <c r="D22" t="s">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="E22" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="F22" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
+        <v>71</v>
+      </c>
+      <c r="G22" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
       <c r="A23" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="B23" t="s">
-        <v>19</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>86</v>
+        <v>22</v>
+      </c>
+      <c r="C23" t="s">
+        <v>23</v>
       </c>
       <c r="D23" t="s">
-        <v>66</v>
+        <v>92</v>
       </c>
       <c r="E23" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="F23" t="s">
-        <v>68</v>
+        <v>71</v>
+      </c>
+      <c r="G23" t="s">
+        <v>72</v>
       </c>
     </row>
   </sheetData>

--- a/Gravedigger2026/Assets/ConfigTables/Mode2/Excel/挖坟_坟墓品质定义表_Dig_GraveQualityConfig.xlsx
+++ b/Gravedigger2026/Assets/ConfigTables/Mode2/Excel/挖坟_坟墓品质定义表_Dig_GraveQualityConfig.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="77">
   <si>
     <t>坟墓品质ID</t>
   </si>
@@ -106,7 +106,7 @@
     <t>1</t>
   </si>
   <si>
-    <t>BP_Head_Undead_1;10000;2|BP_Arm_Undead_2;10000;2</t>
+    <t>BP_Head_Undead_0;2000;1|BP_Torso_Undead_0;2000;1|BP_Arm_Undead_Warrior;2000;1|BP_Arm_Undead_0;2000;1|BP_Leg_Undead_0;2000;1</t>
   </si>
   <si>
     <t>GraveIcon_Q1_High</t>
@@ -121,7 +121,7 @@
     <t>Q2</t>
   </si>
   <si>
-    <t>BP_Torso_Undead_1;10000;2|BP_Leg_Undead_2;10000;2</t>
+    <t>BP_Head_Undead_0;2000;1|BP_Torso_Undead_0;2000;1|BP_Arm_Undead_Archer;2000;1|BP_Arm_Undead_0;2000;1|BP_Leg_Undead_0;2000;1</t>
   </si>
   <si>
     <t>GraveIcon_Q2_High</t>
@@ -136,7 +136,7 @@
     <t>Q3</t>
   </si>
   <si>
-    <t>BP_Arm_Undead_Warrior;10000;1|BP_Head_Demon;10000;2</t>
+    <t>BP_Head_Undead_0;2000;1|BP_Torso_Undead_0;2000;1|BP_Arm_Undead_Rogue;2000;1|BP_Arm_Undead_0;2000;1|BP_Leg_Undead_0;2000;1</t>
   </si>
   <si>
     <t>GraveIcon_Q3_High</t>
@@ -151,7 +151,7 @@
     <t>Q4</t>
   </si>
   <si>
-    <t>BP_Arm_Undead_Archer;10000;1|BP_Torso_Demon;10000;2</t>
+    <t>BP_Head_Undead_1;4000;1|BP_Torso_Undead_1;4000;1|BP_Arm_Undead_Warrior;4000;1|BP_Arm_Undead_1;4000;1|BP_Leg_Undead_1;4000;1</t>
   </si>
   <si>
     <t>GraveIcon_Q4_High</t>
@@ -166,7 +166,7 @@
     <t>Q5</t>
   </si>
   <si>
-    <t>BP_Arm_Undead_Mage;10000;1|BP_Arm_Demon;10000;2</t>
+    <t>BP_Head_Undead_1;1200;1|BP_Torso_Undead_1;1200;1|BP_Arm_Undead_Archer;1200;1|BP_Arm_Undead_1;1200;1|BP_Leg_Undead_1;1200;1</t>
   </si>
   <si>
     <t>GraveIcon_Q5_High</t>
@@ -181,7 +181,7 @@
     <t>Q6</t>
   </si>
   <si>
-    <t>BP_Arm_Undead_Rogue;10000;1|BP_Leg_Demon;10000;2</t>
+    <t>BP_Head_Undead_1;1200;1|BP_Torso_Undead_1;1200;1|BP_Arm_Undead_Rogue;1200;1|BP_Arm_Undead_1;1200;1|BP_Leg_Undead_1;1200;1</t>
   </si>
   <si>
     <t>GraveIcon_Q6_High</t>
@@ -196,7 +196,7 @@
     <t>Q7</t>
   </si>
   <si>
-    <t>BP_Arm_Undead_Guardian;10000;1</t>
+    <t>BP_Arm_Undead_Guardian;4000;1|BP_Arm_Undead_Berserker;4000;1|BP_Head_Undead_2;4000;1|BP_Torso_Undead_2;4000;1|BP_Arm_Undead_2;4000;1|BP_Leg_Undead_2;4000;1</t>
   </si>
   <si>
     <t>GraveIcon_Q7_High</t>
@@ -211,7 +211,7 @@
     <t>Q8</t>
   </si>
   <si>
-    <t>BP_Arm_Undead_BombMaster;10000;1</t>
+    <t>BP_Arm_Undead_BombMaster;1200;1|BP_Arm_Undead_Longbowman;1200;1|BP_Head_Undead_2;1200;1|BP_Torso_Undead_2;1200;1|BP_Arm_Undead_2;1200;1|BP_Leg_Undead_2;1200;1</t>
   </si>
   <si>
     <t>GraveIcon_Q8_High</t>
@@ -226,7 +226,7 @@
     <t>Q9</t>
   </si>
   <si>
-    <t>BP_Arm_Undead_IceMage;10000;1</t>
+    <t>BP_Arm_Undead_FireMage;1200;1|BP_Arm_Undead_IceMage;1200;1|BP_Head_Undead_2;1200;1|BP_Torso_Undead_2;1200;1|BP_Arm_Undead_2;1200;1|BP_Leg_Undead_2;1200;1</t>
   </si>
   <si>
     <t>GraveIcon_Q9_High</t>
@@ -241,9 +241,6 @@
     <t>Q10</t>
   </si>
   <si>
-    <t>BP_Arm_Undead_Brawler;10000;1</t>
-  </si>
-  <si>
     <t>GraveIcon_Q10_High</t>
   </si>
   <si>
@@ -256,61 +253,16 @@
     <t>Q11</t>
   </si>
   <si>
-    <t>BP_Arm_Undead_Berserker;10000;1</t>
-  </si>
-  <si>
     <t>Q12</t>
   </si>
   <si>
-    <t>BP_Arm_Undead_Longbowman;10000;1</t>
-  </si>
-  <si>
     <t>Q13</t>
   </si>
   <si>
-    <t>BP_Arm_Undead_FireMage;10000;1</t>
-  </si>
-  <si>
     <t>Q14</t>
   </si>
   <si>
-    <t>BP_Arm_Undead_Shadowblade;10000;1</t>
-  </si>
-  <si>
     <t>Q15</t>
-  </si>
-  <si>
-    <t>BP_Arm_Angel_Paladin;10000;1</t>
-  </si>
-  <si>
-    <t>Q16</t>
-  </si>
-  <si>
-    <t>BP_Arm_Demon_DarkMage;10000;1</t>
-  </si>
-  <si>
-    <t>Q17</t>
-  </si>
-  <si>
-    <t>BP_Arm_Undead_1;10000;2|BP_Head_Angel;10000;2</t>
-  </si>
-  <si>
-    <t>Q18</t>
-  </si>
-  <si>
-    <t>BP_Leg_Undead_1;10000;2|BP_Torso_Angel;10000;2</t>
-  </si>
-  <si>
-    <t>Q19</t>
-  </si>
-  <si>
-    <t>BP_Head_Undead_2;10000;2|BP_Arm_Angel;10000;2</t>
-  </si>
-  <si>
-    <t>Q20</t>
-  </si>
-  <si>
-    <t>BP_Torso_Undead_2;10000;2|BP_Leg_Angel;10000;2</t>
   </si>
 </sst>
 </file>
@@ -476,7 +428,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -486,6 +438,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -806,7 +764,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
@@ -830,16 +788,16 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="6">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="6">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="7">
@@ -848,91 +806,92 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="8">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0">
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="12" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="14" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="15" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="16" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="18" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="19" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="20" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="22" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="23" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="24" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="26" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="27" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="28" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="30" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="31" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="34" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1279,7 +1238,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
   <cols>
     <col min="4" max="4" width="35.25" customWidth="1"/>
@@ -1354,7 +1313,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" ht="16" customHeight="1" spans="1:7">
       <c r="A4" t="s">
         <v>21</v>
       </c>
@@ -1364,7 +1323,7 @@
       <c r="C4" t="s">
         <v>23</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="2" t="s">
         <v>24</v>
       </c>
       <c r="E4" t="s">
@@ -1387,7 +1346,7 @@
       <c r="C5" t="s">
         <v>23</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="2" t="s">
         <v>29</v>
       </c>
       <c r="E5" t="s">
@@ -1410,7 +1369,7 @@
       <c r="C6" t="s">
         <v>23</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" s="2" t="s">
         <v>34</v>
       </c>
       <c r="E6" t="s">
@@ -1433,7 +1392,7 @@
       <c r="C7" t="s">
         <v>23</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D7" s="2" t="s">
         <v>39</v>
       </c>
       <c r="E7" t="s">
@@ -1456,7 +1415,7 @@
       <c r="C8" t="s">
         <v>23</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D8" s="2" t="s">
         <v>44</v>
       </c>
       <c r="E8" t="s">
@@ -1479,7 +1438,7 @@
       <c r="C9" t="s">
         <v>23</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D9" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E9" t="s">
@@ -1502,7 +1461,7 @@
       <c r="C10" t="s">
         <v>23</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D10" s="2" t="s">
         <v>54</v>
       </c>
       <c r="E10" t="s">
@@ -1525,7 +1484,7 @@
       <c r="C11" t="s">
         <v>23</v>
       </c>
-      <c r="D11" t="s">
+      <c r="D11" s="2" t="s">
         <v>59</v>
       </c>
       <c r="E11" t="s">
@@ -1548,7 +1507,7 @@
       <c r="C12" t="s">
         <v>23</v>
       </c>
-      <c r="D12" t="s">
+      <c r="D12" s="2" t="s">
         <v>64</v>
       </c>
       <c r="E12" t="s">
@@ -1571,22 +1530,22 @@
       <c r="C13" t="s">
         <v>23</v>
       </c>
-      <c r="D13" t="s">
+      <c r="D13" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E13" t="s">
         <v>69</v>
       </c>
-      <c r="E13" t="s">
+      <c r="F13" t="s">
         <v>70</v>
       </c>
-      <c r="F13" t="s">
+      <c r="G13" t="s">
         <v>71</v>
-      </c>
-      <c r="G13" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B14" t="s">
         <v>22</v>
@@ -1594,22 +1553,22 @@
       <c r="C14" t="s">
         <v>23</v>
       </c>
-      <c r="D14" t="s">
-        <v>74</v>
+      <c r="D14" s="2" t="s">
+        <v>44</v>
       </c>
       <c r="E14" t="s">
+        <v>69</v>
+      </c>
+      <c r="F14" t="s">
         <v>70</v>
       </c>
-      <c r="F14" t="s">
+      <c r="G14" t="s">
         <v>71</v>
-      </c>
-      <c r="G14" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B15" t="s">
         <v>22</v>
@@ -1617,22 +1576,22 @@
       <c r="C15" t="s">
         <v>23</v>
       </c>
-      <c r="D15" t="s">
-        <v>76</v>
+      <c r="D15" s="2" t="s">
+        <v>49</v>
       </c>
       <c r="E15" t="s">
+        <v>69</v>
+      </c>
+      <c r="F15" t="s">
         <v>70</v>
       </c>
-      <c r="F15" t="s">
+      <c r="G15" t="s">
         <v>71</v>
-      </c>
-      <c r="G15" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="B16" t="s">
         <v>22</v>
@@ -1640,22 +1599,22 @@
       <c r="C16" t="s">
         <v>23</v>
       </c>
-      <c r="D16" t="s">
-        <v>78</v>
+      <c r="D16" s="2" t="s">
+        <v>54</v>
       </c>
       <c r="E16" t="s">
+        <v>69</v>
+      </c>
+      <c r="F16" t="s">
         <v>70</v>
       </c>
-      <c r="F16" t="s">
+      <c r="G16" t="s">
         <v>71</v>
-      </c>
-      <c r="G16" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B17" t="s">
         <v>22</v>
@@ -1663,22 +1622,22 @@
       <c r="C17" t="s">
         <v>23</v>
       </c>
-      <c r="D17" t="s">
-        <v>80</v>
+      <c r="D17" s="2" t="s">
+        <v>59</v>
       </c>
       <c r="E17" t="s">
+        <v>69</v>
+      </c>
+      <c r="F17" t="s">
         <v>70</v>
       </c>
-      <c r="F17" t="s">
+      <c r="G17" t="s">
         <v>71</v>
-      </c>
-      <c r="G17" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="B18" t="s">
         <v>22</v>
@@ -1686,132 +1645,17 @@
       <c r="C18" t="s">
         <v>23</v>
       </c>
-      <c r="D18" t="s">
-        <v>82</v>
+      <c r="D18" s="2" t="s">
+        <v>64</v>
       </c>
       <c r="E18" t="s">
+        <v>69</v>
+      </c>
+      <c r="F18" t="s">
         <v>70</v>
       </c>
-      <c r="F18" t="s">
+      <c r="G18" t="s">
         <v>71</v>
-      </c>
-      <c r="G18" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19" t="s">
-        <v>83</v>
-      </c>
-      <c r="B19" t="s">
-        <v>22</v>
-      </c>
-      <c r="C19" t="s">
-        <v>23</v>
-      </c>
-      <c r="D19" t="s">
-        <v>84</v>
-      </c>
-      <c r="E19" t="s">
-        <v>70</v>
-      </c>
-      <c r="F19" t="s">
-        <v>71</v>
-      </c>
-      <c r="G19" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20" t="s">
-        <v>85</v>
-      </c>
-      <c r="B20" t="s">
-        <v>22</v>
-      </c>
-      <c r="C20" t="s">
-        <v>23</v>
-      </c>
-      <c r="D20" t="s">
-        <v>86</v>
-      </c>
-      <c r="E20" t="s">
-        <v>70</v>
-      </c>
-      <c r="F20" t="s">
-        <v>71</v>
-      </c>
-      <c r="G20" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21" t="s">
-        <v>87</v>
-      </c>
-      <c r="B21" t="s">
-        <v>22</v>
-      </c>
-      <c r="C21" t="s">
-        <v>23</v>
-      </c>
-      <c r="D21" t="s">
-        <v>88</v>
-      </c>
-      <c r="E21" t="s">
-        <v>70</v>
-      </c>
-      <c r="F21" t="s">
-        <v>71</v>
-      </c>
-      <c r="G21" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22" t="s">
-        <v>89</v>
-      </c>
-      <c r="B22" t="s">
-        <v>22</v>
-      </c>
-      <c r="C22" t="s">
-        <v>23</v>
-      </c>
-      <c r="D22" t="s">
-        <v>90</v>
-      </c>
-      <c r="E22" t="s">
-        <v>70</v>
-      </c>
-      <c r="F22" t="s">
-        <v>71</v>
-      </c>
-      <c r="G22" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23" t="s">
-        <v>91</v>
-      </c>
-      <c r="B23" t="s">
-        <v>22</v>
-      </c>
-      <c r="C23" t="s">
-        <v>23</v>
-      </c>
-      <c r="D23" t="s">
-        <v>92</v>
-      </c>
-      <c r="E23" t="s">
-        <v>70</v>
-      </c>
-      <c r="F23" t="s">
-        <v>71</v>
-      </c>
-      <c r="G23" t="s">
-        <v>72</v>
       </c>
     </row>
   </sheetData>

--- a/Gravedigger2026/Assets/ConfigTables/Mode2/Excel/挖坟_坟墓品质定义表_Dig_GraveQualityConfig.xlsx
+++ b/Gravedigger2026/Assets/ConfigTables/Mode2/Excel/挖坟_坟墓品质定义表_Dig_GraveQualityConfig.xlsx
@@ -106,7 +106,7 @@
     <t>1</t>
   </si>
   <si>
-    <t>BP_Head_Undead_0;2000;1|BP_Torso_Undead_0;2000;1|BP_Arm_Undead_Warrior;2000;1|BP_Arm_Undead_0;2000;1|BP_Leg_Undead_0;2000;1</t>
+    <t>BP_Head_Undead_0;2000;1|BP_Torso_Undead_0;2000;1|BP_Arm_Undead_Warrior_0;2000;1|BP_Arm_Undead_0;2000;1|BP_Leg_Undead_0;2000;1</t>
   </si>
   <si>
     <t>GraveIcon_Q1_High</t>
@@ -121,7 +121,7 @@
     <t>Q2</t>
   </si>
   <si>
-    <t>BP_Head_Undead_0;2000;1|BP_Torso_Undead_0;2000;1|BP_Arm_Undead_Archer;2000;1|BP_Arm_Undead_0;2000;1|BP_Leg_Undead_0;2000;1</t>
+    <t>BP_Head_Undead_0;2000;1|BP_Torso_Undead_0;2000;1|BP_Arm_Undead_Archer_0;2000;1|BP_Arm_Undead_0;2000;1|BP_Leg_Undead_0;2000;1</t>
   </si>
   <si>
     <t>GraveIcon_Q2_High</t>
@@ -136,7 +136,7 @@
     <t>Q3</t>
   </si>
   <si>
-    <t>BP_Head_Undead_0;2000;1|BP_Torso_Undead_0;2000;1|BP_Arm_Undead_Rogue;2000;1|BP_Arm_Undead_0;2000;1|BP_Leg_Undead_0;2000;1</t>
+    <t>BP_Head_Undead_0;2000;1|BP_Torso_Undead_0;2000;1|BP_Arm_Undead_Rogue_0;2000;1|BP_Arm_Undead_0;2000;1|BP_Leg_Undead_0;2000;1</t>
   </si>
   <si>
     <t>GraveIcon_Q3_High</t>
@@ -1241,7 +1241,7 @@
   <dimension ref="A1:G18"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
   <cols>
-    <col min="4" max="4" width="35.25" customWidth="1"/>
+    <col min="4" max="4" width="130.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">

--- a/Gravedigger2026/Assets/ConfigTables/Mode2/Excel/挖坟_坟墓品质定义表_Dig_GraveQualityConfig.xlsx
+++ b/Gravedigger2026/Assets/ConfigTables/Mode2/Excel/挖坟_坟墓品质定义表_Dig_GraveQualityConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12255" tabRatio="750"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="136">
   <si>
     <t>坟墓品质ID</t>
   </si>
@@ -253,16 +253,193 @@
     <t>Q11</t>
   </si>
   <si>
+    <t>GraveIcon_Q11_High</t>
+  </si>
+  <si>
+    <t>GraveIcon_Q11_Mid</t>
+  </si>
+  <si>
+    <t>GraveIcon_Q11_Low</t>
+  </si>
+  <si>
     <t>Q12</t>
   </si>
   <si>
+    <t>GraveIcon_Q12_High</t>
+  </si>
+  <si>
+    <t>GraveIcon_Q12_Mid</t>
+  </si>
+  <si>
+    <t>GraveIcon_Q12_Low</t>
+  </si>
+  <si>
     <t>Q13</t>
   </si>
   <si>
+    <t>GraveIcon_Q13_High</t>
+  </si>
+  <si>
+    <t>GraveIcon_Q13_Mid</t>
+  </si>
+  <si>
+    <t>GraveIcon_Q13_Low</t>
+  </si>
+  <si>
     <t>Q14</t>
   </si>
   <si>
+    <t>GraveIcon_Q14_High</t>
+  </si>
+  <si>
+    <t>GraveIcon_Q14_Mid</t>
+  </si>
+  <si>
+    <t>GraveIcon_Q14_Low</t>
+  </si>
+  <si>
     <t>Q15</t>
+  </si>
+  <si>
+    <t>GraveIcon_Q15_High</t>
+  </si>
+  <si>
+    <t>GraveIcon_Q15_Mid</t>
+  </si>
+  <si>
+    <t>GraveIcon_Q15_Low</t>
+  </si>
+  <si>
+    <t>Q16</t>
+  </si>
+  <si>
+    <t>GraveIcon_Q16_High</t>
+  </si>
+  <si>
+    <t>GraveIcon_Q16_Mid</t>
+  </si>
+  <si>
+    <t>GraveIcon_Q16_Low</t>
+  </si>
+  <si>
+    <t>Q17</t>
+  </si>
+  <si>
+    <t>GraveIcon_Q17_High</t>
+  </si>
+  <si>
+    <t>GraveIcon_Q17_Mid</t>
+  </si>
+  <si>
+    <t>GraveIcon_Q17_Low</t>
+  </si>
+  <si>
+    <t>Q18</t>
+  </si>
+  <si>
+    <t>GraveIcon_Q18_High</t>
+  </si>
+  <si>
+    <t>GraveIcon_Q18_Mid</t>
+  </si>
+  <si>
+    <t>GraveIcon_Q18_Low</t>
+  </si>
+  <si>
+    <t>Q19</t>
+  </si>
+  <si>
+    <t>GraveIcon_Q19_High</t>
+  </si>
+  <si>
+    <t>GraveIcon_Q19_Mid</t>
+  </si>
+  <si>
+    <t>GraveIcon_Q19_Low</t>
+  </si>
+  <si>
+    <t>Q20</t>
+  </si>
+  <si>
+    <t>GraveIcon_Q20_High</t>
+  </si>
+  <si>
+    <t>GraveIcon_Q20_Mid</t>
+  </si>
+  <si>
+    <t>GraveIcon_Q20_Low</t>
+  </si>
+  <si>
+    <t>Q21</t>
+  </si>
+  <si>
+    <t>GraveIcon_Q21_High</t>
+  </si>
+  <si>
+    <t>GraveIcon_Q21_Mid</t>
+  </si>
+  <si>
+    <t>GraveIcon_Q21_Low</t>
+  </si>
+  <si>
+    <t>Q22</t>
+  </si>
+  <si>
+    <t>GraveIcon_Q22_High</t>
+  </si>
+  <si>
+    <t>GraveIcon_Q22_Mid</t>
+  </si>
+  <si>
+    <t>GraveIcon_Q22_Low</t>
+  </si>
+  <si>
+    <t>Q23</t>
+  </si>
+  <si>
+    <t>GraveIcon_Q23_High</t>
+  </si>
+  <si>
+    <t>GraveIcon_Q23_Mid</t>
+  </si>
+  <si>
+    <t>GraveIcon_Q23_Low</t>
+  </si>
+  <si>
+    <t>Q24</t>
+  </si>
+  <si>
+    <t>GraveIcon_Q24_High</t>
+  </si>
+  <si>
+    <t>GraveIcon_Q24_Mid</t>
+  </si>
+  <si>
+    <t>GraveIcon_Q24_Low</t>
+  </si>
+  <si>
+    <t>Q25</t>
+  </si>
+  <si>
+    <t>GraveIcon_Q25_High</t>
+  </si>
+  <si>
+    <t>GraveIcon_Q25_Mid</t>
+  </si>
+  <si>
+    <t>GraveIcon_Q25_Low</t>
+  </si>
+  <si>
+    <t>Q26</t>
+  </si>
+  <si>
+    <t>GraveIcon_Q26_High</t>
+  </si>
+  <si>
+    <t>GraveIcon_Q26_Mid</t>
+  </si>
+  <si>
+    <t>GraveIcon_Q26_Low</t>
   </si>
 </sst>
 </file>
@@ -275,10 +452,17 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -758,140 +942,144 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="33" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="34" borderId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="34" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1238,10 +1426,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
   <cols>
     <col min="4" max="4" width="130.5" customWidth="1"/>
+    <col min="5" max="6" width="16.375" customWidth="1"/>
+    <col min="7" max="7" width="17" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -1317,13 +1507,13 @@
       <c r="A4" t="s">
         <v>21</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C4" t="s">
-        <v>23</v>
-      </c>
-      <c r="D4" s="2" t="s">
+      <c r="C4" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4" s="3" t="s">
         <v>24</v>
       </c>
       <c r="E4" t="s">
@@ -1340,13 +1530,13 @@
       <c r="A5" t="s">
         <v>28</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D5" s="2" t="s">
+      <c r="C5" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D5" s="3" t="s">
         <v>29</v>
       </c>
       <c r="E5" t="s">
@@ -1363,13 +1553,13 @@
       <c r="A6" t="s">
         <v>33</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C6" t="s">
-        <v>23</v>
-      </c>
-      <c r="D6" s="2" t="s">
+      <c r="C6" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D6" s="3" t="s">
         <v>34</v>
       </c>
       <c r="E6" t="s">
@@ -1386,13 +1576,13 @@
       <c r="A7" t="s">
         <v>38</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C7" t="s">
-        <v>23</v>
-      </c>
-      <c r="D7" s="2" t="s">
+      <c r="C7" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D7" s="3" t="s">
         <v>39</v>
       </c>
       <c r="E7" t="s">
@@ -1409,13 +1599,13 @@
       <c r="A8" t="s">
         <v>43</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C8" t="s">
-        <v>23</v>
-      </c>
-      <c r="D8" s="2" t="s">
+      <c r="C8" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D8" s="3" t="s">
         <v>44</v>
       </c>
       <c r="E8" t="s">
@@ -1432,13 +1622,13 @@
       <c r="A9" t="s">
         <v>48</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C9" t="s">
-        <v>23</v>
-      </c>
-      <c r="D9" s="2" t="s">
+      <c r="C9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D9" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E9" t="s">
@@ -1455,13 +1645,13 @@
       <c r="A10" t="s">
         <v>53</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C10" t="s">
-        <v>23</v>
-      </c>
-      <c r="D10" s="2" t="s">
+      <c r="C10" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D10" s="3" t="s">
         <v>54</v>
       </c>
       <c r="E10" t="s">
@@ -1478,13 +1668,13 @@
       <c r="A11" t="s">
         <v>58</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C11" t="s">
-        <v>23</v>
-      </c>
-      <c r="D11" s="2" t="s">
+      <c r="C11" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D11" s="3" t="s">
         <v>59</v>
       </c>
       <c r="E11" t="s">
@@ -1501,13 +1691,13 @@
       <c r="A12" t="s">
         <v>63</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C12" t="s">
-        <v>23</v>
-      </c>
-      <c r="D12" s="2" t="s">
+      <c r="C12" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D12" s="3" t="s">
         <v>64</v>
       </c>
       <c r="E12" t="s">
@@ -1524,13 +1714,13 @@
       <c r="A13" t="s">
         <v>68</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C13" t="s">
-        <v>23</v>
-      </c>
-      <c r="D13" s="2" t="s">
+      <c r="C13" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D13" s="3" t="s">
         <v>39</v>
       </c>
       <c r="E13" t="s">
@@ -1547,115 +1737,368 @@
       <c r="A14" t="s">
         <v>72</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C14" t="s">
-        <v>23</v>
-      </c>
-      <c r="D14" s="2" t="s">
+      <c r="C14" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D14" s="3" t="s">
         <v>44</v>
       </c>
       <c r="E14" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="F14" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="G14" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15" t="s">
-        <v>73</v>
-      </c>
-      <c r="B15" t="s">
+        <v>76</v>
+      </c>
+      <c r="B15" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C15" t="s">
-        <v>23</v>
-      </c>
-      <c r="D15" s="2" t="s">
+      <c r="C15" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D15" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E15" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="F15" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="G15" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16" t="s">
-        <v>74</v>
-      </c>
-      <c r="B16" t="s">
+        <v>80</v>
+      </c>
+      <c r="B16" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C16" t="s">
-        <v>23</v>
-      </c>
-      <c r="D16" s="2" t="s">
+      <c r="C16" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D16" s="3" t="s">
         <v>54</v>
       </c>
       <c r="E16" t="s">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="F16" t="s">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="G16" t="s">
-        <v>71</v>
+        <v>83</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17" t="s">
-        <v>75</v>
-      </c>
-      <c r="B17" t="s">
+        <v>84</v>
+      </c>
+      <c r="B17" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C17" t="s">
-        <v>23</v>
-      </c>
-      <c r="D17" s="2" t="s">
+      <c r="C17" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D17" s="3" t="s">
         <v>59</v>
       </c>
       <c r="E17" t="s">
-        <v>69</v>
+        <v>85</v>
       </c>
       <c r="F17" t="s">
-        <v>70</v>
+        <v>86</v>
       </c>
       <c r="G17" t="s">
-        <v>71</v>
+        <v>87</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18" t="s">
-        <v>76</v>
-      </c>
-      <c r="B18" t="s">
+        <v>88</v>
+      </c>
+      <c r="B18" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C18" t="s">
-        <v>23</v>
-      </c>
-      <c r="D18" s="2" t="s">
+      <c r="C18" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D18" s="3" t="s">
         <v>64</v>
       </c>
       <c r="E18" t="s">
-        <v>69</v>
+        <v>89</v>
       </c>
       <c r="F18" t="s">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="G18" t="s">
-        <v>71</v>
+        <v>91</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19" t="s">
+        <v>92</v>
+      </c>
+      <c r="B19" s="2">
+        <v>26</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E19" t="s">
+        <v>93</v>
+      </c>
+      <c r="F19" t="s">
+        <v>94</v>
+      </c>
+      <c r="G19" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20" t="s">
+        <v>96</v>
+      </c>
+      <c r="B20" s="2">
+        <v>26</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E20" t="s">
+        <v>97</v>
+      </c>
+      <c r="F20" t="s">
+        <v>98</v>
+      </c>
+      <c r="G20" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21" t="s">
+        <v>100</v>
+      </c>
+      <c r="B21" s="2">
+        <v>26</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E21" t="s">
+        <v>101</v>
+      </c>
+      <c r="F21" t="s">
+        <v>102</v>
+      </c>
+      <c r="G21" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22" t="s">
+        <v>104</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E22" t="s">
+        <v>105</v>
+      </c>
+      <c r="F22" t="s">
+        <v>106</v>
+      </c>
+      <c r="G22" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23" t="s">
+        <v>108</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E23" t="s">
+        <v>109</v>
+      </c>
+      <c r="F23" t="s">
+        <v>110</v>
+      </c>
+      <c r="G23" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24" t="s">
+        <v>112</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E24" t="s">
+        <v>113</v>
+      </c>
+      <c r="F24" t="s">
+        <v>114</v>
+      </c>
+      <c r="G24" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25" t="s">
+        <v>116</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E25" t="s">
+        <v>117</v>
+      </c>
+      <c r="F25" t="s">
+        <v>118</v>
+      </c>
+      <c r="G25" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26" t="s">
+        <v>120</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E26" t="s">
+        <v>121</v>
+      </c>
+      <c r="F26" t="s">
+        <v>122</v>
+      </c>
+      <c r="G26" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27" t="s">
+        <v>124</v>
+      </c>
+      <c r="B27" s="2">
+        <v>26</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E27" t="s">
+        <v>125</v>
+      </c>
+      <c r="F27" t="s">
+        <v>126</v>
+      </c>
+      <c r="G27" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28" t="s">
+        <v>128</v>
+      </c>
+      <c r="B28" s="2">
+        <v>26</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E28" t="s">
+        <v>129</v>
+      </c>
+      <c r="F28" t="s">
+        <v>130</v>
+      </c>
+      <c r="G28" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29" t="s">
+        <v>132</v>
+      </c>
+      <c r="B29" s="2">
+        <v>26</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E29" t="s">
+        <v>133</v>
+      </c>
+      <c r="F29" t="s">
+        <v>134</v>
+      </c>
+      <c r="G29" t="s">
+        <v>135</v>
       </c>
     </row>
   </sheetData>

--- a/Gravedigger2026/Assets/ConfigTables/Mode2/Excel/挖坟_坟墓品质定义表_Dig_GraveQualityConfig.xlsx
+++ b/Gravedigger2026/Assets/ConfigTables/Mode2/Excel/挖坟_坟墓品质定义表_Dig_GraveQualityConfig.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="152">
   <si>
     <t>坟墓品质ID</t>
   </si>
@@ -313,6 +313,9 @@
     <t>Q16</t>
   </si>
   <si>
+    <t>BP_Arm_Human_Guardian;4000;1|BP_Arm_Human_Berserker;4000;1|BP_Head_Human_2;4000;1|BP_Torso_Human_2;4000;1|BP_Arm_Human_2;4000;1|BP_Leg_Human_2;4000;1</t>
+  </si>
+  <si>
     <t>GraveIcon_Q16_High</t>
   </si>
   <si>
@@ -325,6 +328,9 @@
     <t>Q17</t>
   </si>
   <si>
+    <t>BP_Arm_Human_BombMaster;4000;1|BP_Arm_Human_Longbowman;4000;1|BP_Head_Human_2;4000;1|BP_Torso_Human_2;4000;1|BP_Arm_Human_2;4000;1|BP_Leg_Human_2;4000;1</t>
+  </si>
+  <si>
     <t>GraveIcon_Q17_High</t>
   </si>
   <si>
@@ -337,6 +343,9 @@
     <t>Q18</t>
   </si>
   <si>
+    <t>BP_Arm_Human_Brawler;4000;1|BP_Arm_Human_Shadowblade;4000;1|BP_Head_Human_2;4000;1|BP_Torso_Human_2;4000;1|BP_Arm_Human_2;4000;1|BP_Leg_Human_2;4000;1</t>
+  </si>
+  <si>
     <t>GraveIcon_Q18_High</t>
   </si>
   <si>
@@ -349,6 +358,9 @@
     <t>Q19</t>
   </si>
   <si>
+    <t>BP_Arm_Human_IceMage;4000;1|BP_Arm_Human_FireMage;4000;1|BP_Head_Human_2;4000;1|BP_Torso_Human_2;4000;1|BP_Arm_Human_2;4000;1|BP_Leg_Human_2;4000;1</t>
+  </si>
+  <si>
     <t>GraveIcon_Q19_High</t>
   </si>
   <si>
@@ -361,6 +373,9 @@
     <t>Q20</t>
   </si>
   <si>
+    <t>BP_Arm_Elf_Guardian;4000;1|BP_Arm_Elf_Berserker;4000;1|BP_Head_Elf_2;4000;1|BP_Torso_Elf_2;4000;1|BP_Arm_Elf_2;4000;1|BP_Leg_Elf_2;4000;1</t>
+  </si>
+  <si>
     <t>GraveIcon_Q20_High</t>
   </si>
   <si>
@@ -373,6 +388,9 @@
     <t>Q21</t>
   </si>
   <si>
+    <t>BP_Arm_Elf_BombMaster;4000;1|BP_Arm_Elf_Longbowman;4000;1|BP_Head_Elf_2;4000;1|BP_Torso_Elf_2;4000;1|BP_Arm_Elf_2;4000;1|BP_Leg_Elf_2;4000;1</t>
+  </si>
+  <si>
     <t>GraveIcon_Q21_High</t>
   </si>
   <si>
@@ -385,6 +403,9 @@
     <t>Q22</t>
   </si>
   <si>
+    <t>BP_Arm_Elf_IceMage;4000;1|BP_Arm_Elf_FireMage;4000;1|BP_Head_Elf_2;4000;1|BP_Torso_Elf_2;4000;1|BP_Arm_Elf_2;4000;1|BP_Leg_Elf_2;4000;1</t>
+  </si>
+  <si>
     <t>GraveIcon_Q22_High</t>
   </si>
   <si>
@@ -397,6 +418,9 @@
     <t>Q23</t>
   </si>
   <si>
+    <t>BP_Arm_Elf_Brawler;4000;1|BP_Arm_Elf_Shadowblade;4000;1|BP_Head_Elf_2;4000;1|BP_Torso_Elf_2;4000;1|BP_Arm_Elf_2;4000;1|BP_Leg_Elf_2;4000;1</t>
+  </si>
+  <si>
     <t>GraveIcon_Q23_High</t>
   </si>
   <si>
@@ -409,6 +433,9 @@
     <t>Q24</t>
   </si>
   <si>
+    <t>BP_Arm_Orc_Guardian;4000;1|BP_Arm_Orc_Berserker;4000;1|BP_Head_Orc_2;4000;1|BP_Torso_Orc_2;4000;1|BP_Arm_Orc_2;4000;1|BP_Leg_Orc_2;4000;1</t>
+  </si>
+  <si>
     <t>GraveIcon_Q24_High</t>
   </si>
   <si>
@@ -421,6 +448,9 @@
     <t>Q25</t>
   </si>
   <si>
+    <t>BP_Arm_Orc_BombMaster;4000;1|BP_Arm_Orc_Longbowman;4000;1|BP_Head_Orc_2;4000;1|BP_Torso_Orc_2;4000;1|BP_Arm_Orc_2;4000;1|BP_Leg_Orc_2;4000;1</t>
+  </si>
+  <si>
     <t>GraveIcon_Q25_High</t>
   </si>
   <si>
@@ -433,6 +463,9 @@
     <t>Q26</t>
   </si>
   <si>
+    <t>BP_Arm_Orc_IceMage;4000;1|BP_Arm_Orc_FireMage;4000;1|BP_Head_Orc_2;4000;1|BP_Torso_Orc_2;4000;1|BP_Arm_Orc_2;4000;1|BP_Leg_Orc_2;4000;1</t>
+  </si>
+  <si>
     <t>GraveIcon_Q26_High</t>
   </si>
   <si>
@@ -440,6 +473,21 @@
   </si>
   <si>
     <t>GraveIcon_Q26_Low</t>
+  </si>
+  <si>
+    <t>Q27</t>
+  </si>
+  <si>
+    <t>BP_Arm_Orc_Brawler;4000;1|BP_Arm_Orc_Shadowblade;4000;1|BP_Head_Orc_2;4000;1|BP_Torso_Orc_2;4000;1|BP_Arm_Orc_2;4000;1|BP_Leg_Orc_2;4000;1</t>
+  </si>
+  <si>
+    <t>GraveIcon_Q27_High</t>
+  </si>
+  <si>
+    <t>GraveIcon_Q27_Mid</t>
+  </si>
+  <si>
+    <t>GraveIcon_Q27_Low</t>
   </si>
 </sst>
 </file>
@@ -462,7 +510,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -612,7 +659,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="37">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -628,6 +675,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -948,7 +1007,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
@@ -972,16 +1031,16 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="6">
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="6">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="7">
@@ -990,96 +1049,98 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="8">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="34" borderId="0">
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="34" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="35" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="36" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1426,7 +1487,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:G30"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
   <cols>
     <col min="4" max="4" width="130.5" customWidth="1"/>
@@ -1849,7 +1910,7 @@
       </c>
     </row>
     <row r="19" spans="1:7">
-      <c r="A19" t="s">
+      <c r="A19" s="4" t="s">
         <v>92</v>
       </c>
       <c r="B19" s="2">
@@ -1858,22 +1919,22 @@
       <c r="C19" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="D19" s="4" t="s">
-        <v>24</v>
+      <c r="D19" s="5" t="s">
+        <v>93</v>
       </c>
       <c r="E19" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F19" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G19" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="20" spans="1:7">
-      <c r="A20" t="s">
-        <v>96</v>
+      <c r="A20" s="4" t="s">
+        <v>97</v>
       </c>
       <c r="B20" s="2">
         <v>26</v>
@@ -1881,22 +1942,22 @@
       <c r="C20" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="D20" s="4" t="s">
-        <v>24</v>
+      <c r="D20" s="5" t="s">
+        <v>98</v>
       </c>
       <c r="E20" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F20" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G20" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="21" spans="1:7">
-      <c r="A21" t="s">
-        <v>100</v>
+      <c r="A21" s="4" t="s">
+        <v>102</v>
       </c>
       <c r="B21" s="2">
         <v>26</v>
@@ -1904,22 +1965,22 @@
       <c r="C21" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="D21" s="4" t="s">
-        <v>24</v>
+      <c r="D21" s="5" t="s">
+        <v>103</v>
       </c>
       <c r="E21" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="F21" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="G21" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
     </row>
     <row r="22" spans="1:7">
-      <c r="A22" t="s">
-        <v>104</v>
+      <c r="A22" s="4" t="s">
+        <v>107</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>22</v>
@@ -1927,22 +1988,22 @@
       <c r="C22" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="D22" s="4" t="s">
-        <v>24</v>
+      <c r="D22" s="5" t="s">
+        <v>108</v>
       </c>
       <c r="E22" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="F22" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="G22" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
     </row>
     <row r="23" spans="1:7">
-      <c r="A23" t="s">
-        <v>108</v>
+      <c r="A23" s="6" t="s">
+        <v>112</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>22</v>
@@ -1950,22 +2011,22 @@
       <c r="C23" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="D23" s="4" t="s">
-        <v>24</v>
+      <c r="D23" s="5" t="s">
+        <v>113</v>
       </c>
       <c r="E23" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="F23" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="G23" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
     </row>
     <row r="24" spans="1:7">
-      <c r="A24" t="s">
-        <v>112</v>
+      <c r="A24" s="6" t="s">
+        <v>117</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>22</v>
@@ -1973,22 +2034,22 @@
       <c r="C24" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="D24" s="4" t="s">
-        <v>24</v>
+      <c r="D24" s="5" t="s">
+        <v>118</v>
       </c>
       <c r="E24" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="F24" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="G24" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
     </row>
     <row r="25" spans="1:7">
-      <c r="A25" t="s">
-        <v>116</v>
+      <c r="A25" s="6" t="s">
+        <v>122</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>22</v>
@@ -1996,22 +2057,22 @@
       <c r="C25" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="D25" s="4" t="s">
-        <v>24</v>
+      <c r="D25" s="5" t="s">
+        <v>123</v>
       </c>
       <c r="E25" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="F25" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="G25" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
     </row>
     <row r="26" spans="1:7">
-      <c r="A26" t="s">
-        <v>120</v>
+      <c r="A26" s="6" t="s">
+        <v>127</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>22</v>
@@ -2019,22 +2080,22 @@
       <c r="C26" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="D26" s="4" t="s">
-        <v>24</v>
+      <c r="D26" s="5" t="s">
+        <v>128</v>
       </c>
       <c r="E26" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="F26" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="G26" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
     </row>
     <row r="27" spans="1:7">
-      <c r="A27" t="s">
-        <v>124</v>
+      <c r="A27" s="4" t="s">
+        <v>132</v>
       </c>
       <c r="B27" s="2">
         <v>26</v>
@@ -2042,22 +2103,22 @@
       <c r="C27" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="D27" s="4" t="s">
-        <v>24</v>
+      <c r="D27" s="5" t="s">
+        <v>133</v>
       </c>
       <c r="E27" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="F27" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="G27" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
     </row>
     <row r="28" spans="1:7">
-      <c r="A28" t="s">
-        <v>128</v>
+      <c r="A28" s="4" t="s">
+        <v>137</v>
       </c>
       <c r="B28" s="2">
         <v>26</v>
@@ -2065,22 +2126,22 @@
       <c r="C28" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="D28" s="4" t="s">
-        <v>24</v>
+      <c r="D28" s="5" t="s">
+        <v>138</v>
       </c>
       <c r="E28" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="F28" t="s">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="G28" t="s">
-        <v>131</v>
+        <v>141</v>
       </c>
     </row>
     <row r="29" spans="1:7">
-      <c r="A29" t="s">
-        <v>132</v>
+      <c r="A29" s="4" t="s">
+        <v>142</v>
       </c>
       <c r="B29" s="2">
         <v>26</v>
@@ -2088,17 +2149,40 @@
       <c r="C29" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="D29" s="4" t="s">
-        <v>24</v>
+      <c r="D29" s="5" t="s">
+        <v>143</v>
       </c>
       <c r="E29" t="s">
-        <v>133</v>
+        <v>144</v>
       </c>
       <c r="F29" t="s">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="G29" t="s">
-        <v>135</v>
+        <v>146</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="A30" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="B30" s="2">
+        <v>26</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D30" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="E30" t="s">
+        <v>149</v>
+      </c>
+      <c r="F30" t="s">
+        <v>150</v>
+      </c>
+      <c r="G30" t="s">
+        <v>151</v>
       </c>
     </row>
   </sheetData>

--- a/Gravedigger2026/Assets/ConfigTables/Mode2/Excel/挖坟_坟墓品质定义表_Dig_GraveQualityConfig.xlsx
+++ b/Gravedigger2026/Assets/ConfigTables/Mode2/Excel/挖坟_坟墓品质定义表_Dig_GraveQualityConfig.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Work\Cursor\Gravedigger2026\Gravedigger2026\Gravedigger2026\Assets\ConfigTables\Mode2\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\CursorGame_Git\Gravedigger2026\Gravedigger2026\Assets\ConfigTables\Mode2\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255" tabRatio="750"/>
+    <workbookView windowWidth="25600" windowHeight="12080" tabRatio="750"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="157">
   <si>
     <t>坟墓品质ID</t>
   </si>
@@ -488,6 +488,21 @@
   </si>
   <si>
     <t>GraveIcon_Q27_Low</t>
+  </si>
+  <si>
+    <t>Q101</t>
+  </si>
+  <si>
+    <t>Spirit;6000;2|Spirit;2000;4|Spirit;1500;8|Spirit;500;16</t>
+  </si>
+  <si>
+    <t>GraveIcon_Q28_High</t>
+  </si>
+  <si>
+    <t>GraveIcon_Q28_Mid</t>
+  </si>
+  <si>
+    <t>GraveIcon_Q28_Low</t>
   </si>
 </sst>
 </file>
@@ -659,7 +674,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="37">
+  <fills count="38">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -675,6 +690,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1" tint="0.5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1007,7 +1028,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
@@ -1031,16 +1052,16 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="6">
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="6">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="7">
@@ -1049,89 +1070,89 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="8">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0">
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="15" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="17" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="19" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="21" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="23" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="25" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="27" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="29" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="31" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="33" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="34" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="34" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="35" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="36" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="36" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="37" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1139,8 +1160,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1487,11 +1509,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G30"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
+  <dimension ref="A1:G31"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="6"/>
   <cols>
-    <col min="4" max="4" width="130.5" customWidth="1"/>
-    <col min="5" max="6" width="16.375" customWidth="1"/>
+    <col min="1" max="1" width="12.7272727272727" customWidth="1"/>
+    <col min="4" max="4" width="60" customWidth="1"/>
+    <col min="5" max="5" width="20.0909090909091" customWidth="1"/>
+    <col min="6" max="6" width="16.3727272727273" customWidth="1"/>
     <col min="7" max="7" width="17" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1577,13 +1601,13 @@
       <c r="D4" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E4" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="F4" t="s">
+      <c r="F4" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="G4" t="s">
+      <c r="G4" s="4" t="s">
         <v>27</v>
       </c>
     </row>
@@ -1600,13 +1624,13 @@
       <c r="D5" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E5" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="F5" t="s">
+      <c r="F5" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="G5" t="s">
+      <c r="G5" s="4" t="s">
         <v>32</v>
       </c>
     </row>
@@ -1623,13 +1647,13 @@
       <c r="D6" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="E6" t="s">
+      <c r="E6" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="F6" t="s">
+      <c r="F6" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="G6" t="s">
+      <c r="G6" s="4" t="s">
         <v>37</v>
       </c>
     </row>
@@ -1646,13 +1670,13 @@
       <c r="D7" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="E7" t="s">
+      <c r="E7" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="F7" t="s">
+      <c r="F7" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="G7" t="s">
+      <c r="G7" s="4" t="s">
         <v>42</v>
       </c>
     </row>
@@ -1669,13 +1693,13 @@
       <c r="D8" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="E8" t="s">
+      <c r="E8" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="F8" t="s">
+      <c r="F8" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="G8" t="s">
+      <c r="G8" s="4" t="s">
         <v>47</v>
       </c>
     </row>
@@ -1692,13 +1716,13 @@
       <c r="D9" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="E9" t="s">
+      <c r="E9" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="F9" t="s">
+      <c r="F9" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="G9" t="s">
+      <c r="G9" s="4" t="s">
         <v>52</v>
       </c>
     </row>
@@ -1715,13 +1739,13 @@
       <c r="D10" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="E10" t="s">
+      <c r="E10" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="F10" t="s">
+      <c r="F10" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="G10" t="s">
+      <c r="G10" s="4" t="s">
         <v>57</v>
       </c>
     </row>
@@ -1738,13 +1762,13 @@
       <c r="D11" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="E11" t="s">
+      <c r="E11" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="F11" t="s">
+      <c r="F11" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="G11" t="s">
+      <c r="G11" s="4" t="s">
         <v>62</v>
       </c>
     </row>
@@ -1761,13 +1785,13 @@
       <c r="D12" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="E12" t="s">
+      <c r="E12" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="F12" t="s">
+      <c r="F12" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="G12" t="s">
+      <c r="G12" s="4" t="s">
         <v>67</v>
       </c>
     </row>
@@ -1784,13 +1808,13 @@
       <c r="D13" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="E13" t="s">
+      <c r="E13" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="F13" t="s">
+      <c r="F13" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="G13" t="s">
+      <c r="G13" s="4" t="s">
         <v>71</v>
       </c>
     </row>
@@ -1807,13 +1831,13 @@
       <c r="D14" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="E14" t="s">
+      <c r="E14" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="F14" t="s">
+      <c r="F14" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="G14" t="s">
+      <c r="G14" s="4" t="s">
         <v>75</v>
       </c>
     </row>
@@ -1830,13 +1854,13 @@
       <c r="D15" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="E15" t="s">
+      <c r="E15" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="F15" t="s">
+      <c r="F15" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="G15" t="s">
+      <c r="G15" s="4" t="s">
         <v>79</v>
       </c>
     </row>
@@ -1853,13 +1877,13 @@
       <c r="D16" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="E16" t="s">
+      <c r="E16" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="F16" t="s">
+      <c r="F16" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="G16" t="s">
+      <c r="G16" s="4" t="s">
         <v>83</v>
       </c>
     </row>
@@ -1876,13 +1900,13 @@
       <c r="D17" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="E17" t="s">
+      <c r="E17" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="F17" t="s">
+      <c r="F17" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="G17" t="s">
+      <c r="G17" s="4" t="s">
         <v>87</v>
       </c>
     </row>
@@ -1899,18 +1923,18 @@
       <c r="D18" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="E18" t="s">
+      <c r="E18" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="F18" t="s">
+      <c r="F18" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="G18" t="s">
+      <c r="G18" s="4" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="19" spans="1:7">
-      <c r="A19" s="4" t="s">
+      <c r="A19" s="5" t="s">
         <v>92</v>
       </c>
       <c r="B19" s="2">
@@ -1919,21 +1943,21 @@
       <c r="C19" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="D19" s="5" t="s">
+      <c r="D19" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="E19" t="s">
+      <c r="E19" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="F19" t="s">
+      <c r="F19" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="G19" t="s">
+      <c r="G19" s="4" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="20" spans="1:7">
-      <c r="A20" s="4" t="s">
+      <c r="A20" s="5" t="s">
         <v>97</v>
       </c>
       <c r="B20" s="2">
@@ -1942,21 +1966,21 @@
       <c r="C20" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="D20" s="5" t="s">
+      <c r="D20" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="E20" t="s">
+      <c r="E20" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="F20" t="s">
+      <c r="F20" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="G20" t="s">
+      <c r="G20" s="4" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="21" spans="1:7">
-      <c r="A21" s="4" t="s">
+      <c r="A21" s="5" t="s">
         <v>102</v>
       </c>
       <c r="B21" s="2">
@@ -1965,21 +1989,21 @@
       <c r="C21" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="D21" s="5" t="s">
+      <c r="D21" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="E21" t="s">
+      <c r="E21" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="F21" t="s">
+      <c r="F21" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="G21" t="s">
+      <c r="G21" s="4" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="22" spans="1:7">
-      <c r="A22" s="4" t="s">
+      <c r="A22" s="5" t="s">
         <v>107</v>
       </c>
       <c r="B22" s="2" t="s">
@@ -1988,21 +2012,21 @@
       <c r="C22" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="D22" s="5" t="s">
+      <c r="D22" s="6" t="s">
         <v>108</v>
       </c>
-      <c r="E22" t="s">
+      <c r="E22" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="F22" t="s">
+      <c r="F22" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="G22" t="s">
+      <c r="G22" s="4" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="23" spans="1:7">
-      <c r="A23" s="6" t="s">
+      <c r="A23" s="7" t="s">
         <v>112</v>
       </c>
       <c r="B23" s="2" t="s">
@@ -2011,21 +2035,21 @@
       <c r="C23" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="D23" s="5" t="s">
+      <c r="D23" s="6" t="s">
         <v>113</v>
       </c>
-      <c r="E23" t="s">
+      <c r="E23" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="F23" t="s">
+      <c r="F23" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="G23" t="s">
+      <c r="G23" s="4" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="24" spans="1:7">
-      <c r="A24" s="6" t="s">
+      <c r="A24" s="7" t="s">
         <v>117</v>
       </c>
       <c r="B24" s="2" t="s">
@@ -2034,21 +2058,21 @@
       <c r="C24" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="D24" s="5" t="s">
+      <c r="D24" s="6" t="s">
         <v>118</v>
       </c>
-      <c r="E24" t="s">
+      <c r="E24" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="F24" t="s">
+      <c r="F24" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="G24" t="s">
+      <c r="G24" s="4" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="25" spans="1:7">
-      <c r="A25" s="6" t="s">
+      <c r="A25" s="7" t="s">
         <v>122</v>
       </c>
       <c r="B25" s="2" t="s">
@@ -2057,21 +2081,21 @@
       <c r="C25" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="D25" s="5" t="s">
+      <c r="D25" s="6" t="s">
         <v>123</v>
       </c>
-      <c r="E25" t="s">
+      <c r="E25" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="F25" t="s">
+      <c r="F25" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="G25" t="s">
+      <c r="G25" s="4" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="26" spans="1:7">
-      <c r="A26" s="6" t="s">
+      <c r="A26" s="7" t="s">
         <v>127</v>
       </c>
       <c r="B26" s="2" t="s">
@@ -2080,21 +2104,21 @@
       <c r="C26" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="D26" s="5" t="s">
+      <c r="D26" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="E26" t="s">
+      <c r="E26" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="F26" t="s">
+      <c r="F26" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="G26" t="s">
+      <c r="G26" s="4" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="27" spans="1:7">
-      <c r="A27" s="4" t="s">
+      <c r="A27" s="5" t="s">
         <v>132</v>
       </c>
       <c r="B27" s="2">
@@ -2103,21 +2127,21 @@
       <c r="C27" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="D27" s="5" t="s">
+      <c r="D27" s="6" t="s">
         <v>133</v>
       </c>
-      <c r="E27" t="s">
+      <c r="E27" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="F27" t="s">
+      <c r="F27" s="4" t="s">
         <v>135</v>
       </c>
-      <c r="G27" t="s">
+      <c r="G27" s="4" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="28" spans="1:7">
-      <c r="A28" s="4" t="s">
+      <c r="A28" s="5" t="s">
         <v>137</v>
       </c>
       <c r="B28" s="2">
@@ -2126,21 +2150,21 @@
       <c r="C28" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="D28" s="5" t="s">
+      <c r="D28" s="6" t="s">
         <v>138</v>
       </c>
-      <c r="E28" t="s">
+      <c r="E28" s="4" t="s">
         <v>139</v>
       </c>
-      <c r="F28" t="s">
+      <c r="F28" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="G28" t="s">
+      <c r="G28" s="4" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="29" spans="1:7">
-      <c r="A29" s="4" t="s">
+      <c r="A29" s="5" t="s">
         <v>142</v>
       </c>
       <c r="B29" s="2">
@@ -2149,21 +2173,21 @@
       <c r="C29" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="D29" s="5" t="s">
+      <c r="D29" s="6" t="s">
         <v>143</v>
       </c>
-      <c r="E29" t="s">
+      <c r="E29" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="F29" t="s">
+      <c r="F29" s="4" t="s">
         <v>145</v>
       </c>
-      <c r="G29" t="s">
+      <c r="G29" s="4" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="30" spans="1:7">
-      <c r="A30" s="4" t="s">
+      <c r="A30" s="5" t="s">
         <v>147</v>
       </c>
       <c r="B30" s="2">
@@ -2172,17 +2196,40 @@
       <c r="C30" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="D30" s="5" t="s">
+      <c r="D30" s="6" t="s">
         <v>148</v>
       </c>
-      <c r="E30" t="s">
+      <c r="E30" s="4" t="s">
         <v>149</v>
       </c>
-      <c r="F30" t="s">
+      <c r="F30" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="G30" t="s">
+      <c r="G30" s="4" t="s">
         <v>151</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="A31" t="s">
+        <v>152</v>
+      </c>
+      <c r="B31" s="2">
+        <v>100</v>
+      </c>
+      <c r="C31" s="2">
+        <v>2</v>
+      </c>
+      <c r="D31" t="s">
+        <v>153</v>
+      </c>
+      <c r="E31" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="F31" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="G31" s="4" t="s">
+        <v>156</v>
       </c>
     </row>
   </sheetData>
